--- a/Cost Breakdown/CostBreakdown.xlsx
+++ b/Cost Breakdown/CostBreakdown.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/Cost Breakdown/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06C48DBD-8120-4A61-B94D-149F3D8EF4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{06C48DBD-8120-4A61-B94D-149F3D8EF4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B58D71-5131-419B-8AE6-DBD08CD8EA5B}"/>
   <bookViews>
-    <workbookView xWindow="-26880" yWindow="1740" windowWidth="17280" windowHeight="9960" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C684E4FE-65D8-41BB-8319-3046AEA9131B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Aircraft Cost Grand Total" sheetId="1" r:id="rId1"/>
+    <sheet name="Per Assembly Cost --&gt;" sheetId="6" r:id="rId2"/>
+    <sheet name="Avionics BOM" sheetId="2" r:id="rId3"/>
+    <sheet name="Structures BOM" sheetId="3" r:id="rId4"/>
+    <sheet name="Mechanisms BOM" sheetId="4" r:id="rId5"/>
+    <sheet name="Miscellaneous BOM" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -405,6 +410,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{547011CB-CEF2-42FC-B0AC-2D8C8531DD67}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -412,7 +420,84 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF71F69-4424-432D-BD60-B85CB6840641}">
+  <sheetPr>
+    <tabColor theme="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AD7834-7C47-4D2E-884E-E19556DA306C}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348EDAF7-A5D7-4152-836A-B9FBFC5EBBCA}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7042592B-214A-4A35-B2C1-2B5CEB3A02A7}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27457C91-B27A-4B31-A491-3C36347AA9A2}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F9431A864773547893222757859AEDB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d93b3794edbd64c1f12ce1859fb2ebb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c440327c-db0c-40f7-973b-7bc2ae283ce2" xmlns:ns4="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ab198344f7607dd971ab6c53863418c3" ns3:_="" ns4:_="">
     <xsd:import namespace="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
@@ -637,24 +722,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c440327c-db0c-40f7-973b-7bc2ae283ce2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C5615A-B0FE-40B8-955A-C3851BD0A604}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -671,29 +764,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140E0E22-42B5-4B4A-934D-04548B25B00B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120B44-02FC-4D2A-B0A5-AADC531A6E78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c440327c-db0c-40f7-973b-7bc2ae283ce2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bf09d50-f695-4e18-a2ec-955b0ff6d5dc"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>